--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_yearly.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -956,12 +956,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -982,38 +982,42 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>39364</v>
+        <v>43880</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>43913</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40582</v>
+        <v>44055</v>
       </c>
       <c r="M4" t="n">
-        <v>840</v>
+        <v>122</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.2902464771828115</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.2902464771828115</v>
       </c>
       <c r="P4" t="n">
-        <v>839</v>
+        <v>121</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1774193046859526</v>
+        <v>0.117717550534894</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
@@ -1023,25 +1027,25 @@
       </c>
       <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.2902464771828115</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>-0.4019616742567396</v>
+        <v>-0.2902464771828115</v>
       </c>
       <c r="Y4" t="b">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>485</v>
+        <v>99</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" s="3" t="n">
-        <v>0.6721336358454439</v>
+        <v>0.4089398190385176</v>
       </c>
       <c r="AD4" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1052,27 +1056,27 @@
         </is>
       </c>
       <c r="AF4" s="3" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>5/6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>4/6</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>6/6</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>3/6</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>3/6</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
@@ -1084,11 +1088,11 @@
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1106,7 +1110,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1137,32 +1141,32 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43880</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43913</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>44055</v>
+        <v>40582</v>
       </c>
       <c r="M5" t="n">
-        <v>122</v>
+        <v>840</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2902464771828115</v>
+        <v>-0.4028865261537454</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2902464771828115</v>
+        <v>-0.4028865261537454</v>
       </c>
       <c r="P5" t="n">
-        <v>121</v>
+        <v>839</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.117717550534894</v>
+        <v>0.1784433268325409</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
@@ -1172,25 +1176,25 @@
       </c>
       <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" s="3" t="n">
-        <v>-0.2902464771828115</v>
+        <v>-0.4028865261537454</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>-0.2902464771828115</v>
+        <v>-0.4028865261537454</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>99</v>
+        <v>485</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" s="3" t="n">
-        <v>0.4089398190385176</v>
+        <v>0.6747235555724223</v>
       </c>
       <c r="AD5" s="3" t="n">
         <v>0.8333333333333334</v>
@@ -1209,35 +1213,35 @@
         </is>
       </c>
       <c r="AH5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AJ5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>6/6</t>
-        </is>
-      </c>
       <c r="AN5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1255,7 +1259,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1273,49 +1277,45 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>39364</v>
+        <v>36865</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>39881</v>
+        <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40582</v>
+        <v>38399</v>
       </c>
       <c r="M6" t="n">
-        <v>840</v>
+        <v>1053</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4028865261537454</v>
+        <v>-0.3383158398603916</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4028865261537454</v>
+        <v>-0.3383158398603916</v>
       </c>
       <c r="P6" t="n">
-        <v>839</v>
+        <v>1052</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1784433268325409</v>
+        <v>0.1437677861761672</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
@@ -1325,32 +1325,32 @@
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>355</v>
+        <v>405</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" s="3" t="n">
-        <v>-0.4028865261537454</v>
+        <v>-0.3383158398603916</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>-0.4028865261537454</v>
+        <v>-0.3383158398603916</v>
       </c>
       <c r="Y6" t="b">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>485</v>
+        <v>648</v>
       </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" s="3" t="n">
-        <v>0.6747235555724223</v>
+        <v>0.5112950562229124</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
@@ -1370,19 +1370,19 @@
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
@@ -1393,30 +1393,12 @@
           <t>2/6</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1426,7 +1408,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1457,32 +1439,32 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36865</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>38399</v>
+        <v>40637</v>
       </c>
       <c r="M7" t="n">
-        <v>1053</v>
+        <v>878</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.3383158398603916</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.3383158398603916</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="P7" t="n">
-        <v>1052</v>
+        <v>877</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1437677861761672</v>
+        <v>0.1790468553513548</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
@@ -1492,32 +1474,32 @@
       </c>
       <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>405</v>
+        <v>355</v>
       </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" s="3" t="n">
-        <v>-0.3383158398603916</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>-0.3383158398603916</v>
+        <v>-0.4206716948626341</v>
       </c>
       <c r="Y7" t="b">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>648</v>
+        <v>523</v>
       </c>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" s="3" t="n">
-        <v>0.5112950562229124</v>
+        <v>0.7261369609118058</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
@@ -1529,35 +1511,35 @@
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1575,7 +1557,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1593,49 +1575,45 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>39364</v>
+        <v>43437</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>43913</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40637</v>
+        <v>44071</v>
       </c>
       <c r="M8" t="n">
-        <v>878</v>
+        <v>437</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.3150305412703731</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.3150305412703731</v>
       </c>
       <c r="P8" t="n">
-        <v>877</v>
+        <v>436</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1790468553513548</v>
+        <v>0.09908018502521306</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
@@ -1645,32 +1623,32 @@
       </c>
       <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" s="3" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.3150305412703731</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>-0.4206716948626341</v>
+        <v>-0.3150305412703731</v>
       </c>
       <c r="Y8" t="b">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>523</v>
+        <v>111</v>
       </c>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" s="3" t="n">
-        <v>0.7261369609118058</v>
+        <v>0.4599191062542292</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
@@ -1682,61 +1660,43 @@
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
+          <t>3/6</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1746,7 +1706,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1777,32 +1737,32 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43437</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43913</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>44071</v>
+        <v>40581</v>
       </c>
       <c r="M9" t="n">
-        <v>437</v>
+        <v>839</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.3150305412703731</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3150305412703731</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="P9" t="n">
-        <v>436</v>
+        <v>838</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.09908018502521306</v>
+        <v>0.1777961907160987</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
@@ -1812,32 +1772,32 @@
       </c>
       <c r="T9" s="3" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" s="3" t="n">
-        <v>-0.3150305412703731</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-0.3150305412703731</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="Y9" t="b">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>111</v>
+        <v>484</v>
       </c>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" s="3" t="n">
-        <v>0.4599191062542292</v>
+        <v>0.6747235555724218</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
@@ -1849,35 +1809,35 @@
         </is>
       </c>
       <c r="AH9" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2/6</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>4/6</t>
         </is>
       </c>
-      <c r="AJ9" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
       <c r="AN9" s="3" t="n">
-        <v>0.5</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -1886,177 +1846,6 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40581</v>
-      </c>
-      <c r="M10" t="n">
-        <v>839</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="P10" t="n">
-        <v>838</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1777961907160987</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" t="n">
-        <v>355</v>
-      </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="Y10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>484</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" s="3" t="n">
-        <v>0.6747235555724218</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>5/6</t>
-        </is>
-      </c>
-      <c r="AH10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>2/6</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>4/6</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>0/6</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>1/6</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2069,7 +1858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2543,12 +2332,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2558,7 +2347,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2569,41 +2358,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>37460</v>
+        <v>36630</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>37784</v>
+        <v>36641</v>
       </c>
       <c r="M4" t="n">
-        <v>807</v>
+        <v>22</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2092382282226474</v>
+        <v>-0.05121391880486614</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="P4" t="n">
-        <v>281</v>
+        <v>11</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1174267585984309</v>
+        <v>0.03149204818459606</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.07663710450244801</v>
+        <v>0.003467617290759166</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>39364</v>
@@ -2616,38 +2409,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>583</v>
+        <v>16</v>
       </c>
       <c r="X4" t="n">
-        <v>-55</v>
+        <v>-622</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2092382282226474</v>
+        <v>-0.05121391880486614</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.3043384976802425</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>224</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
         <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2646033681577118</v>
+        <v>0.05397836226724029</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.02872309750348744</v>
+        <v>-0.1018925847151763</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.08749770256512879</v>
+        <v>0.24552201198291</v>
       </c>
       <c r="AH4" t="n">
-        <v>-168</v>
+        <v>-386</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2667,7 +2460,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2698,35 +2491,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>36608</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>36630</v>
+        <v>37460</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>36641</v>
+        <v>38012</v>
       </c>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>963</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.05121391880486614</v>
+        <v>-0.2719231189126349</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.3149700650581952</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>733</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.03149204818459606</v>
+        <v>0.128321305658241</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.003467617290759166</v>
+        <v>0.09147525343333868</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>39364</v>
@@ -2739,38 +2532,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>16</v>
+        <v>583</v>
       </c>
       <c r="X5" t="n">
-        <v>-622</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.05121391880486614</v>
+        <v>-0.2719231189126349</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.3149700650581952</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>6</v>
+        <v>380</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
         <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.05397836226724029</v>
+        <v>0.3734813259095995</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1018925847151763</v>
+        <v>-0.01388494857259677</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.24552201198291</v>
+        <v>0.02481281187514128</v>
       </c>
       <c r="AH5" t="n">
-        <v>-386</v>
+        <v>-12</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2790,7 +2583,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2808,24 +2601,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -2835,25 +2624,25 @@
         <v>37460</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38012</v>
+        <v>38028</v>
       </c>
       <c r="M6" t="n">
-        <v>963</v>
+        <v>975</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2719231189126349</v>
+        <v>-0.2967359307877762</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="P6" t="n">
-        <v>733</v>
+        <v>786</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.128321305658241</v>
+        <v>0.1468876731549894</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.09147525343333868</v>
+        <v>0.1053602020059354</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>39364</v>
@@ -2872,48 +2661,40 @@
         <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2719231189126349</v>
+        <v>-0.2967359307877762</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
         <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3734813259095995</v>
+        <v>0.4219409803207652</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.01388494857259677</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.02481281187514128</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.01483814893089067</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.0626848906899875</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>156</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -2925,7 +2706,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2956,7 +2737,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -3048,7 +2829,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3066,24 +2847,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -3093,25 +2870,25 @@
         <v>37460</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>38028</v>
+        <v>38923</v>
       </c>
       <c r="M8" t="n">
-        <v>975</v>
+        <v>1592</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.2545765592642644</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="P8" t="n">
-        <v>786</v>
+        <v>1134</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.1182905634116231</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.1083987621329908</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>39364</v>
@@ -3130,48 +2907,40 @@
         <v>-55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.2545765592642644</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>392</v>
+        <v>1009</v>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
         <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.3415193906606913</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>0.003038560127055348</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.04215937152351179</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>617</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.02872309750348744</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.08749770256512879</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>168</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -3183,7 +2952,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3214,7 +2983,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -3224,25 +2993,25 @@
         <v>37460</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>38923</v>
+        <v>38145</v>
       </c>
       <c r="M9" t="n">
-        <v>1592</v>
+        <v>1055</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2545765592642644</v>
+        <v>-0.2826404536824703</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3031420059512167</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="P9" t="n">
-        <v>1134</v>
+        <v>827</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1182905634116231</v>
+        <v>0.1355407093692397</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1083987621329908</v>
+        <v>0.1011272151808934</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>39364</v>
@@ -3261,32 +3030,32 @@
         <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2545765592642644</v>
+        <v>-0.2826404536824703</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3031420059512167</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1009</v>
+        <v>472</v>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
         <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3415193906606913</v>
+        <v>0.3940011046529841</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.003038560127055348</v>
+        <v>-0.004232986825042043</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.04215937152351179</v>
+        <v>0.0140954771053059</v>
       </c>
       <c r="AH9" t="n">
-        <v>617</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3297,141 +3066,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>38145</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1055</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2826404536824703</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.3250537462336849</v>
-      </c>
-      <c r="P10" t="n">
-        <v>827</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1355407093692397</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.1011272151808934</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>583</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-55</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2826404536824703</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.3250537462336849</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>472</v>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.3940011046529841</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.004232986825042043</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.0140954771053059</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.02449011067844539</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.07340222545982289</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>248</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3444,7 +3078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3922,12 +3556,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3937,7 +3571,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3948,41 +3582,45 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>39881</v>
+        <v>39412</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>40582</v>
+        <v>41306</v>
       </c>
       <c r="M4" t="n">
-        <v>840</v>
+        <v>1338</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="P4" t="n">
-        <v>839</v>
+        <v>1337</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.177419304685953</v>
+        <v>0.03418961092914297</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.09795419063977666</v>
+        <v>0.0238181813106745</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43364</v>
@@ -3995,40 +3633,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>355</v>
+        <v>33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.4019616742567399</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>485</v>
+        <v>1305</v>
       </c>
       <c r="AC4" t="n">
-        <v>-375</v>
+        <v>445</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.6721336358454448</v>
+        <v>0.08090022454844625</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.03226906506364592</v>
+        <v>-0.1064050743927481</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.06327430879694729</v>
+        <v>0.3903907543164622</v>
       </c>
       <c r="AH4" t="n">
-        <v>-259</v>
+        <v>561</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4048,7 +3686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4079,35 +3717,35 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>39412</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>41306</v>
+        <v>40582</v>
       </c>
       <c r="M5" t="n">
-        <v>1338</v>
+        <v>840</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="P5" t="n">
-        <v>1337</v>
+        <v>839</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.03418961092914297</v>
+        <v>0.1784433268325408</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.0238181813106745</v>
+        <v>0.09851955899551319</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43364</v>
@@ -4120,40 +3758,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>33</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>-322</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1305</v>
+        <v>485</v>
       </c>
       <c r="AC5" t="n">
-        <v>445</v>
+        <v>-375</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.08090022454844625</v>
+        <v>0.6747235555724218</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.1064050743927481</v>
+        <v>-0.03170369670790939</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.3903907543164622</v>
+        <v>0.06234945689994187</v>
       </c>
       <c r="AH5" t="n">
-        <v>561</v>
+        <v>-259</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -4173,7 +3811,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4191,24 +3829,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -4218,25 +3852,25 @@
         <v>39881</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>40582</v>
+        <v>40028</v>
       </c>
       <c r="M6" t="n">
-        <v>840</v>
+        <v>457</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="P6" t="n">
-        <v>839</v>
+        <v>456</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1784433268325408</v>
+        <v>0.07583002456742177</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.09851955899551319</v>
+        <v>0.0308957032748606</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43364</v>
@@ -4255,50 +3889,42 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>485</v>
+        <v>102</v>
       </c>
       <c r="AC6" t="n">
-        <v>-375</v>
+        <v>-758</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.6747235555724218</v>
+        <v>0.3508572592271493</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.03170369670790939</v>
+        <v>-0.09932755242856198</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.06234945689994187</v>
+        <v>0.2055066468632141</v>
       </c>
       <c r="AH6" t="n">
-        <v>-259</v>
+        <v>-642</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.0005653683557365341</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.0009248518970054187</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -4310,7 +3936,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4341,7 +3967,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -4351,25 +3977,25 @@
         <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>40028</v>
+        <v>40637</v>
       </c>
       <c r="M7" t="n">
-        <v>457</v>
+        <v>878</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="P7" t="n">
-        <v>456</v>
+        <v>877</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07583002456742177</v>
+        <v>0.1790468553513548</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.0308957032748606</v>
+        <v>0.1010613941521971</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43364</v>
@@ -4388,34 +4014,34 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>102</v>
+        <v>523</v>
       </c>
       <c r="AC7" t="n">
-        <v>-758</v>
+        <v>-337</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3508572592271493</v>
+        <v>0.7261369609118054</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.09932755242856198</v>
+        <v>-0.02916186155122544</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.2055066468632141</v>
+        <v>0.04456428819105318</v>
       </c>
       <c r="AH7" t="n">
-        <v>-642</v>
+        <v>-221</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4435,7 +4061,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4453,52 +4079,48 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>39881</v>
+        <v>40361</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>40637</v>
+        <v>40479</v>
       </c>
       <c r="M8" t="n">
-        <v>878</v>
+        <v>770</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="P8" t="n">
-        <v>877</v>
+        <v>769</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1790468553513548</v>
+        <v>0.04928794849378988</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1010613941521971</v>
+        <v>0.02605506018760135</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43364</v>
@@ -4511,56 +4133,48 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>355</v>
+        <v>688</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AC8" t="n">
-        <v>-337</v>
+        <v>-778</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.7261369609118054</v>
+        <v>0.1671720463703512</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.02916186155122544</v>
+        <v>-0.1041681955158212</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04456428819105318</v>
+        <v>0.322007701593195</v>
       </c>
       <c r="AH8" t="n">
-        <v>-221</v>
+        <v>-662</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.003107203512420484</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.01871002060589411</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -4572,7 +4186,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4603,35 +4217,35 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>40361</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>40479</v>
+        <v>40581</v>
       </c>
       <c r="M9" t="n">
-        <v>770</v>
+        <v>839</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="P9" t="n">
-        <v>769</v>
+        <v>838</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.04928794849378988</v>
+        <v>0.1777961907160986</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.02605506018760135</v>
+        <v>0.09810389371974938</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43364</v>
@@ -4644,40 +4258,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>688</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AC9" t="n">
-        <v>-778</v>
+        <v>-376</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1671720463703512</v>
+        <v>0.6747235555724218</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.1041681955158212</v>
+        <v>-0.0321193619836732</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.322007701593195</v>
+        <v>0.06234945689994187</v>
       </c>
       <c r="AH9" t="n">
-        <v>-662</v>
+        <v>-260</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4688,143 +4302,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>39364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>40581</v>
-      </c>
-      <c r="M10" t="n">
-        <v>839</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="P10" t="n">
-        <v>838</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1777961907160986</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09810389371974938</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>355</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>484</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>-376</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.6747235555724218</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>-0.0321193619836732</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.06234945689994187</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>-260</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.0001497030799727239</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.0009248518970054187</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4837,7 +4314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5315,12 +4792,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5330,7 +4807,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5341,13 +4818,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -5357,25 +4838,25 @@
         <v>43458</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43563</v>
+        <v>43559</v>
       </c>
       <c r="M4" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.1464423397562968</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="P4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04842997312606301</v>
+        <v>0.04836031164019639</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.03001802059473596</v>
+        <v>0.02975362321475316</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>43880</v>
@@ -5394,34 +4875,34 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.138687252248779</v>
+        <v>-0.1464423397562968</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1434541510678393</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1610184600319384</v>
+        <v>0.1715670148335209</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.000264397379982774</v>
+        <v>-2.42861286636753e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.007755087507518299</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -5441,7 +4922,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5472,7 +4953,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -5488,19 +4969,19 @@
         <v>133</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1464423397562968</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="P5" t="n">
         <v>131</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04836031164019639</v>
+        <v>0.04836031164019643</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02975362321475316</v>
+        <v>0.02975362321475319</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>43880</v>
@@ -5519,10 +5000,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1464423397562968</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -5537,13 +5018,13 @@
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1715670148335209</v>
+        <v>0.1715670148335215</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-2.42861286636753e-17</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -5566,7 +5047,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5584,24 +5065,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -5610,26 +5087,24 @@
       <c r="K6" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L6" s="2" t="n">
-        <v>43559</v>
-      </c>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>133</v>
+        <v>353</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1464423397562972</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724215</v>
       </c>
       <c r="P6" t="n">
-        <v>131</v>
+        <v>352</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.07082544091672376</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.07082544091672376</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>43880</v>
@@ -5638,9 +5113,11 @@
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.03485302458783623</v>
+      </c>
       <c r="W6" t="n">
         <v>64</v>
       </c>
@@ -5648,50 +5125,38 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1464423397562972</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724215</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>69</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-7</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.1715670148335213</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>0.04107181770197057</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="3" t="n">
-        <v>-0.000264397379982774</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.007755087507518299</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -5703,7 +5168,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5734,7 +5199,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -5743,24 +5208,26 @@
       <c r="K7" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>43585</v>
+      </c>
       <c r="M7" t="n">
-        <v>353</v>
+        <v>150</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1464423397562972</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="P7" t="n">
-        <v>352</v>
+        <v>148</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.07082544091672376</v>
+        <v>0.0472512693456853</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.07082544091672376</v>
+        <v>0.03086031270421815</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>43880</v>
@@ -5769,11 +5236,9 @@
         <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-0.03485302458783623</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
         <v>64</v>
       </c>
@@ -5781,33 +5246,37 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1464423397562972</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1715670148335213</v>
+        <v>0.1715670148335215</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.04107181770197057</v>
+        <v>0.001106689489464963</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17</v>
+      </c>
       <c r="AI7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" s="3" t="inlineStr"/>
       <c r="AK7" s="3" t="inlineStr"/>
@@ -5824,7 +5293,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5842,24 +5311,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -5868,26 +5333,24 @@
       <c r="K8" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L8" s="2" t="n">
-        <v>43585</v>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>150</v>
+        <v>353</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1464423397562969</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724218</v>
       </c>
       <c r="P8" t="n">
-        <v>148</v>
+        <v>352</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.0472512693456853</v>
+        <v>0.07082544091672391</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.03086031270421815</v>
+        <v>0.07082544091672391</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>43880</v>
@@ -5896,9 +5359,11 @@
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.03485302458783579</v>
+      </c>
       <c r="W8" t="n">
         <v>64</v>
       </c>
@@ -5906,50 +5371,38 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.1464423397562969</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.1465009124724218</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>86</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.1715670148335211</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.001106689489464963</v>
+        <v>0.04107181770197072</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>17</v>
-      </c>
+        <v>3.33066907387547e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.0008422921094821886</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.007755087507518299</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -5961,7 +5414,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5992,7 +5445,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -6001,24 +5454,26 @@
       <c r="K9" s="2" t="n">
         <v>43458</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
+        <v>43585</v>
+      </c>
       <c r="M9" t="n">
-        <v>353</v>
+        <v>150</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1464423397562969</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="P9" t="n">
-        <v>352</v>
+        <v>148</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.07082544091672391</v>
+        <v>0.0472512693456853</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.07082544091672391</v>
+        <v>0.03086031270421815</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>43880</v>
@@ -6027,11 +5482,9 @@
         <v>0</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>-0.03485302458783579</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
         <v>64</v>
       </c>
@@ -6039,33 +5492,37 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1464423397562969</v>
+        <v>-0.1464423397562973</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>86</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1715670148335211</v>
+        <v>0.1715670148335215</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.04107181770197072</v>
+        <v>0.001106689489464963</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>3.33066907387547e-16</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>17</v>
+      </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="inlineStr"/>
       <c r="AK9" s="3" t="inlineStr"/>
@@ -6073,143 +5530,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43364</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>43585</v>
-      </c>
-      <c r="M10" t="n">
-        <v>150</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.1464423397562973</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.1465009124724216</v>
-      </c>
-      <c r="P10" t="n">
-        <v>148</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.0472512693456853</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.03086031270421815</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>64</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.1464423397562973</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.1465009124724216</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>86</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.1715670148335215</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.001106689489464963</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.0008422921094821886</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.007755087507518299</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6222,7 +5542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6700,12 +6020,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6715,7 +6035,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6726,13 +6046,17 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
@@ -6748,19 +6072,19 @@
         <v>122</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="P4" t="n">
         <v>121</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1125125693043114</v>
+        <v>0.1177175505348944</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05731448931557177</v>
+        <v>0.05996593388725455</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>44564</v>
@@ -6779,10 +6103,10 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2845422493289217</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
@@ -6797,13 +6121,13 @@
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.3977065718584074</v>
+        <v>0.4089398190385181</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.002651444571682815</v>
+        <v>-3.469446951953614e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.005704227853890242</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -6826,7 +6150,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6857,7 +6181,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
@@ -6873,19 +6197,19 @@
         <v>122</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="P5" t="n">
         <v>121</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.05996593388725455</v>
+        <v>0.05996593388725459</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>44564</v>
@@ -6904,10 +6228,10 @@
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
@@ -6922,13 +6246,13 @@
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4089398190385181</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-3.469446951953614e-17</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -6951,7 +6275,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6969,24 +6293,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -7011,10 +6331,10 @@
         <v>121</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1177175505348944</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05996593388725459</v>
+        <v>0.05996593388725456</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>44564</v>
@@ -7054,7 +6374,7 @@
         <v>0.4089398190385185</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>0</v>
@@ -7065,18 +6385,10 @@
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0.002651444571682815</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>-0.005704227853890242</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="inlineStr"/>
       <c r="AO6" s="3" t="inlineStr"/>
     </row>
@@ -7088,7 +6400,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7119,7 +6431,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -7144,10 +6456,10 @@
         <v>121</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.05996593388725456</v>
+        <v>0.05996593388725459</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>44564</v>
@@ -7187,7 +6499,7 @@
         <v>0.4089398190385185</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
@@ -7213,7 +6525,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -7231,24 +6543,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
@@ -7264,19 +6572,19 @@
         <v>122</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="P8" t="n">
         <v>121</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1177175505348945</v>
+        <v>0.1177175505348944</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05996593388725459</v>
+        <v>0.05996593388725454</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>44564</v>
@@ -7295,10 +6603,10 @@
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
@@ -7313,13 +6621,13 @@
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.4089398190385187</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0</v>
+        <v>-4.85722573273506e-17</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -7327,18 +6635,10 @@
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.002651444571682815</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.005704227853890242</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -7350,7 +6650,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -7381,7 +6681,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
@@ -7397,19 +6697,19 @@
         <v>122</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="P9" t="n">
         <v>121</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1177175505348944</v>
+        <v>0.1177175505348945</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.05996593388725454</v>
+        <v>0.05996593388725459</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>44564</v>
@@ -7428,10 +6728,10 @@
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
@@ -7446,13 +6746,13 @@
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4089398190385187</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-4.85722573273506e-17</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -7466,143 +6766,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>43880</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M10" t="n">
-        <v>122</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P10" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>23</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.4089398190385185</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0.002651444571682815</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>-0.005704227853890242</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7615,7 +6778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8093,12 +7256,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8108,7 +7271,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8119,87 +7282,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45182</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>425</v>
+        <v>513</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.006696816304247677</v>
       </c>
       <c r="P4" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.135142485096232</v>
+        <v>0.0003872733026600608</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.09955472383307543</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-195</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>-220</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.006640031856356587</v>
+        <v>-0.09291469197671884</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.009858841505368088</v>
+        <v>0.2382824194485816</v>
       </c>
       <c r="AH4" t="n">
-        <v>42</v>
+        <v>-188</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8208,8 +7371,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.2383076748178463</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.1920793993641633</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8219,7 +7386,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8250,77 +7417,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45182</v>
+      </c>
       <c r="M5" t="n">
-        <v>513</v>
+        <v>425</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.006696816304247677</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.0003872733026600608</v>
+        <v>0.135142485096232</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.09955472383307543</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AC5" t="n">
-        <v>-220</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.09291469197671884</v>
+        <v>0.006640031856356587</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.2382824194485816</v>
+        <v>0.009858841505368088</v>
       </c>
       <c r="AH5" t="n">
-        <v>-188</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8333,7 +7504,7 @@
         <v>0.2383076748178463</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.1920793993641633</v>
+        <v>-0.02819104197355771</v>
       </c>
     </row>
     <row r="6">
@@ -8344,7 +7515,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -8362,24 +7533,20 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
@@ -8389,25 +7556,25 @@
         <v>44846</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>45182</v>
+        <v>45427</v>
       </c>
       <c r="M6" t="n">
-        <v>425</v>
+        <v>594</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="P6" t="n">
-        <v>424</v>
+        <v>593</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.135142485096232</v>
+        <v>0.1332546418439375</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.09955472383307543</v>
+        <v>0.1160128246035556</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>45707</v>
@@ -8426,56 +7593,44 @@
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>230</v>
+        <v>399</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.006640031856356587</v>
+        <v>0.02309813262683674</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.009858841505368088</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AH6" t="n">
-        <v>42</v>
+        <v>211</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>0.2383076748178463</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.02819104197355771</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8485,7 +7640,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8516,7 +7671,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
@@ -8526,25 +7681,25 @@
         <v>44846</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>45427</v>
+        <v>45182</v>
       </c>
       <c r="M7" t="n">
-        <v>594</v>
+        <v>425</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="P7" t="n">
-        <v>593</v>
+        <v>424</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1332546418439375</v>
+        <v>0.1358689911275819</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1160128246035556</v>
+        <v>0.100089915318289</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>45707</v>
@@ -8563,34 +7718,34 @@
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>399</v>
+        <v>230</v>
       </c>
       <c r="AC7" t="n">
-        <v>179</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.3128225283655466</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.02309813262683674</v>
+        <v>0.007175223341570156</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>211</v>
+        <v>42</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8610,7 +7765,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8628,114 +7783,98 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45182</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>425</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.006696816304248121</v>
       </c>
       <c r="P8" t="n">
-        <v>424</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1358689911275819</v>
+        <v>0.0003872733026600894</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.100089915318289</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.007175223341570156</v>
+        <v>-0.09291469197671884</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0</v>
+        <v>0.2382824194485816</v>
       </c>
       <c r="AH8" t="n">
-        <v>42</v>
+        <v>-188</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0.0005351914852135681</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>-0.009858841505368088</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
       <c r="AO8" s="3" t="inlineStr"/>
     </row>
@@ -8747,7 +7886,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8778,77 +7917,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45182</v>
+      </c>
       <c r="M9" t="n">
-        <v>513</v>
+        <v>425</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.006696816304248121</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.0003872733026600894</v>
+        <v>0.135142485096232</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.09955472383307543</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>45707</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X9" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AC9" t="n">
-        <v>-220</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.09291469197671884</v>
+        <v>0.006640031856356587</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.2382824194485816</v>
+        <v>0.009858841505368088</v>
       </c>
       <c r="AH9" t="n">
-        <v>-188</v>
+        <v>42</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8859,143 +8002,6 @@
       <c r="AM9" t="inlineStr"/>
       <c r="AN9" s="3" t="inlineStr"/>
       <c r="AO9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>44564</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M10" t="n">
-        <v>425</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="P10" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.135142485096232</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.09955472383307543</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>195</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>230</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.2960478980608379</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.006640031856356587</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.009858841505368088</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9008,7 +8014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9486,12 +8492,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mvo</t>
+          <t>hrp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mvo_t_10_lw_minvar</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9501,7 +8507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fallback</t>
+          <t>regime</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9512,87 +8518,87 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>always min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K4" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>45910</v>
-      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>51</v>
+        <v>-55</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.004991043952540582</v>
+        <v>-0.04506184607636846</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.03053508206683808</v>
+        <v>0.1556116196127491</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>-74</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -9601,8 +8607,12 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9612,7 +8622,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9643,77 +8653,81 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45910</v>
+      </c>
       <c r="M5" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="S5" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X5" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AC5" t="n">
-        <v>-55</v>
+        <v>51</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0</v>
+        <v>0.142957119009109</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.04506184607636846</v>
+        <v>0.004991043952540582</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.1556116196127491</v>
+        <v>0.03053508206683808</v>
       </c>
       <c r="AH5" t="n">
-        <v>-74</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -9726,7 +8740,7 @@
         <v>0.06587707306593171</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-0.05707000491572423</v>
+        <v>0.002524191693261901</v>
       </c>
     </row>
     <row r="6">
@@ -9737,7 +8751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9755,119 +8769,103 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>changepoint</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45910</v>
-      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0</v>
       </c>
       <c r="S6" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>51</v>
+        <v>-55</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.004991043952540582</v>
+        <v>-0.04506184607636846</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.03053508206683808</v>
+        <v>0.1556116196127491</v>
       </c>
       <c r="AH6" t="n">
-        <v>32</v>
+        <v>-74</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" s="3" t="n">
         <v>0.06587707306593171</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>0.002524191693261901</v>
+        <v>-0.05707000491572423</v>
       </c>
     </row>
     <row r="7">
@@ -9878,7 +8876,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9909,77 +8907,81 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45910</v>
+      </c>
       <c r="M7" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="S7" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X7" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AC7" t="n">
-        <v>-55</v>
+        <v>51</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0</v>
+        <v>0.142957119009109</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.04506184607636846</v>
+        <v>0.004991043952540582</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.1556116196127491</v>
+        <v>0.03053508206683808</v>
       </c>
       <c r="AH7" t="n">
-        <v>-74</v>
+        <v>32</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -9992,7 +8994,7 @@
         <v>0.06587707306593171</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-0.05707000491572423</v>
+        <v>0.002524191693261901</v>
       </c>
     </row>
     <row r="8">
@@ -10003,7 +9005,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10021,119 +9023,103 @@
           <t>hrp_t_10_lw_ward</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>wasserstein</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>gspc_vix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>min_var</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>45910</v>
-      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.0622368851691482</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.05005289002890904</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-34</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>51</v>
+        <v>-55</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.004991043952540582</v>
+        <v>-0.04506184607636846</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.03053508206683808</v>
+        <v>0.1556116196127491</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>-74</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="b">
-        <v>0</v>
-      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" s="3" t="n">
         <v>0.06587707306593171</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>0.002524191693261901</v>
+        <v>-0.05707000491572423</v>
       </c>
     </row>
     <row r="9">
@@ -10144,7 +9130,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10175,77 +9161,81 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>min_var</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45910</v>
+      </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>0.0622368851691482</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>0.05005289002890904</v>
       </c>
       <c r="S9" s="2" t="n">
         <v>46021</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="X9" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>0</v>
+        <v>-0.125076537545911</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="AC9" t="n">
-        <v>-55</v>
+        <v>51</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0</v>
+        <v>0.142957119009109</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.04506184607636846</v>
+        <v>0.004991043952540582</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.1556116196127491</v>
+        <v>0.03053508206683808</v>
       </c>
       <c r="AH9" t="n">
-        <v>-74</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -10258,147 +9248,6 @@
         <v>0.06587707306593171</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>-0.05707000491572423</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hrp</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yearly</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>regime</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>hrp_t_10_lw_ward</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>mvo_t_10_lw_minvar</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>wasserstein</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>gspc_vix</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>min_var</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>45707</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M10" t="n">
-        <v>140</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P10" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S10" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="T10" t="b">
-        <v>0</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" t="n">
-        <v>34</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="AA10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>106</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>0.142957119009109</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>0.004991043952540582</v>
-      </c>
-      <c r="AG10" s="3" t="n">
-        <v>0.03053508206683808</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AO10" s="3" t="n">
         <v>0.002524191693261901</v>
       </c>
     </row>

--- a/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_yearly.xlsx
+++ b/Paper/_output/_comparison/crisis_analysis_regime/crisis_analysis_variable_hrp_yearly.xlsx
@@ -14,7 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C7" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="timing" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,27 +918,27 @@
         <v>0.8699837092823588</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1048,51 +1049,51 @@
         <v>0.4089398190385176</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>6/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr"/>
@@ -1197,51 +1198,51 @@
         <v>0.6747235555724223</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr"/>
@@ -1346,51 +1347,51 @@
         <v>0.5112950562229124</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>0.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr"/>
@@ -1495,51 +1496,51 @@
         <v>0.7261369609118058</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr"/>
@@ -1644,51 +1645,51 @@
         <v>0.4599191062542292</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr"/>
@@ -1793,51 +1794,51 @@
         <v>0.6747235555724218</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>5/6</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2/6</t>
+          <t>2/7</t>
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>4/6</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1/6</t>
+          <t>1/7</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr"/>
@@ -2142,66 +2143,68 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+        <v>36038</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>36116</v>
+      </c>
       <c r="M2" t="n">
-        <v>1896</v>
+        <v>86</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="P2" t="n">
-        <v>1895</v>
+        <v>85</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.09032004823014485</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2657575172078715</v>
+        <v>0.04076898034342919</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3" t="n">
-        <v>-0.03939252582908814</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X2" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.4859401977791227</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.4862309442441404</v>
+        <v>-0.1697286534192369</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1313</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.9452989626493449</v>
+        <v>0.204425521991354</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -2249,34 +2252,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="M3" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P3" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -2286,29 +2289,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>392</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -2372,34 +2377,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>36630</v>
+        <v>36038</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>36641</v>
+        <v>36105</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.05121391880486614</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P4" t="n">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.03149204818459606</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.003467617290759166</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -2409,38 +2414,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="X4" t="n">
-        <v>-622</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.05121391880486614</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.07939073608397251</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.05397836226724029</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1018925847151763</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.24552201198291</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-386</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -2495,34 +2502,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>38012</v>
+        <v>36105</v>
       </c>
       <c r="M5" t="n">
-        <v>963</v>
+        <v>79</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.2719231189126349</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P5" t="n">
-        <v>733</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.128321305658241</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.09147525343333868</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -2532,38 +2539,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X5" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2719231189126349</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.3149700650581952</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>380</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.3734813259095995</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.01388494857259677</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.02481281187514128</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -2618,34 +2627,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="M6" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P6" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -2655,29 +2664,31 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X6" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>392</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF6" s="3" t="n">
         <v>0</v>
@@ -2741,34 +2752,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>38028</v>
+        <v>36105</v>
       </c>
       <c r="M7" t="n">
-        <v>975</v>
+        <v>79</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="P7" t="n">
-        <v>786</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.1468876731549894</v>
+        <v>0.08993390447450868</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.1053602020059354</v>
+        <v>0.03892731995262652</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -2778,29 +2789,31 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X7" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2967359307877762</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.3383158398603918</v>
+        <v>-0.1629630992012947</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>392</v>
-      </c>
-      <c r="AC7" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4219409803207652</v>
+        <v>0.1946904599376615</v>
       </c>
       <c r="AF7" s="3" t="n">
         <v>0</v>
@@ -2864,75 +2877,73 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36608</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>37460</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>38923</v>
-      </c>
+        <v>35993</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>1592</v>
+        <v>90</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.2545765592642644</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.3031420059512167</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1134</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1182905634116231</v>
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.1083987621329908</v>
+        <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>583</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
+        <v>-31</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
         <v>-55</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>-0.2545765592642644</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>-0.3031420059512167</v>
-      </c>
-      <c r="AA8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1009</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.3415193906606913</v>
+        <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.003038560127055348</v>
+        <v>-0.03892731995262652</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.04215937152351179</v>
+        <v>0.1629630992012947</v>
       </c>
       <c r="AH8" t="n">
-        <v>617</v>
+        <v>-48</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -2941,8 +2952,12 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.2557598127090419</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.1821547032756365</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2987,34 +3002,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>36608</v>
+        <v>35993</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>37460</v>
+        <v>36038</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>38145</v>
+        <v>36105</v>
       </c>
       <c r="M9" t="n">
-        <v>1055</v>
+        <v>79</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.2826404536824703</v>
+        <v>-0.1638829728650903</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.3250537462336849</v>
+        <v>-0.1638829728650903</v>
       </c>
       <c r="P9" t="n">
-        <v>827</v>
+        <v>78</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.1355407093692397</v>
+        <v>0.09202955837544453</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.1011272151808934</v>
+        <v>0.03983441044745568</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>39364</v>
+        <v>36609</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -3024,38 +3039,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>583</v>
+        <v>31</v>
       </c>
       <c r="X9" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2826404536824703</v>
+        <v>-0.1638829728650903</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.3250537462336849</v>
+        <v>-0.1638829728650903</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>472</v>
-      </c>
-      <c r="AC9" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-7</v>
+      </c>
       <c r="AD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.3940011046529841</v>
+        <v>0.1960048265332688</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.004232986825042043</v>
+        <v>0.0009070904948291561</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.0140954771053059</v>
+        <v>-0.0009198736637956451</v>
       </c>
       <c r="AH9" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -3064,8 +3081,12 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.2557598127090419</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>-0.009700156822086914</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3362,68 +3383,66 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.4862309442441404</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1895</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.2658275917027499</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>39364</v>
       </c>
-      <c r="K2" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>41124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1215</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.5035092528573142</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.5040024023286778</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1213</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.2354171526922748</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1562892258388257</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>43364</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
-      </c>
-      <c r="V2" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>-0.03993583465459449</v>
+      </c>
       <c r="W2" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.5035092528573142</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.5040024023286778</v>
+        <v>-0.4862309442441404</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>860</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
+        <v>1313</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>1.014136226616548</v>
+        <v>0.9463998245842093</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -3471,34 +3490,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="M3" t="n">
+        <v>974</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="P3" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>40956</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1099</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.4652359830536872</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1098</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.2062376999383152</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.1302232557034226</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -3508,31 +3527,29 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.4652359830536872</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>744</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-116</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.8699837092823584</v>
+        <v>0.4187401027120015</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -3596,34 +3613,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>36630</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>36641</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.04907332369727813</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.07939073608397251</v>
+      </c>
+      <c r="P4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.03214669869116753</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.003462809127108922</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>39412</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>41306</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1338</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.07484522873722499</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.07484522873722499</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1337</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.03418961092914297</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.0238181813106745</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -3633,40 +3650,38 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="X4" t="n">
-        <v>-322</v>
+        <v>-622</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.04907332369727813</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.07484522873722499</v>
+        <v>-0.07939073608397251</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1305</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>445</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.08090022454844625</v>
+        <v>0.0516057914034751</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.1064050743927481</v>
+        <v>-0.1019249858957527</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.3903907543164622</v>
+        <v>0.2460759442423228</v>
       </c>
       <c r="AH4" t="n">
-        <v>561</v>
+        <v>-386</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -3721,34 +3736,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>38012</v>
+      </c>
+      <c r="M5" t="n">
+        <v>962</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2702804748641048</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.3149700650581954</v>
+      </c>
+      <c r="P5" t="n">
+        <v>717</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1283876100470085</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.09149915672607238</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40582</v>
-      </c>
-      <c r="M5" t="n">
-        <v>840</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="P5" t="n">
-        <v>839</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1784433268325408</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.09851955899551319</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -3758,40 +3773,38 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2702804748641048</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.3149700650581954</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>485</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-375</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.6747235555724218</v>
+        <v>0.3703895339976968</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>-0.03170369670790939</v>
+        <v>-0.01388863829678927</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.06234945689994187</v>
+        <v>0.02486879307549617</v>
       </c>
       <c r="AH5" t="n">
-        <v>-259</v>
+        <v>-12</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -3846,34 +3859,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="M6" t="n">
+        <v>974</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="P6" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>40028</v>
-      </c>
-      <c r="M6" t="n">
-        <v>457</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2597293361904731</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2597293361904731</v>
-      </c>
-      <c r="P6" t="n">
-        <v>456</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.07583002456742177</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.0308957032748606</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -3883,40 +3896,38 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2597293361904731</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>102</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>-758</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3508572592271493</v>
+        <v>0.4187401027120015</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.09932755242856198</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.2055066468632141</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-642</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -3971,34 +3982,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>38028</v>
+      </c>
+      <c r="M7" t="n">
+        <v>974</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2951492679396009</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.3383158398603918</v>
+      </c>
+      <c r="P7" t="n">
+        <v>769</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1469627184408073</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.1053877950228616</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>40637</v>
-      </c>
-      <c r="M7" t="n">
-        <v>878</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.420671694862634</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.420671694862634</v>
-      </c>
-      <c r="P7" t="n">
-        <v>877</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1790468553513548</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.1010613941521971</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -4008,40 +4019,38 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.2951492679396009</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.420671694862634</v>
+        <v>-0.3383158398603918</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>523</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-337</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.7261369609118054</v>
+        <v>0.4187401027120015</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>-0.02916186155122544</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.04456428819105318</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-221</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -4096,34 +4105,34 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>38415</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1241</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.2528947789325902</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.3031420059512167</v>
+      </c>
+      <c r="P8" t="n">
+        <v>774</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1236392338443038</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.1000686259799144</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>40361</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>40479</v>
-      </c>
-      <c r="M8" t="n">
-        <v>770</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.1432282814604922</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.1432282814604922</v>
-      </c>
-      <c r="P8" t="n">
-        <v>769</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.04928794849378988</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.02605506018760135</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
@@ -4133,40 +4142,38 @@
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>688</v>
+        <v>582</v>
       </c>
       <c r="X8" t="n">
-        <v>333</v>
+        <v>-55</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.2528947789325902</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1432282814604922</v>
+        <v>-0.3031420059512167</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>82</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-778</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1671720463703512</v>
+        <v>0.3384995470534558</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.1041681955158212</v>
+        <v>-0.005319169042947214</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.322007701593195</v>
+        <v>0.04225448900701079</v>
       </c>
       <c r="AH8" t="n">
-        <v>-662</v>
+        <v>267</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -4221,34 +4228,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>36609</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>37460</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>38145</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1054</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2810219894515295</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.3250537462336849</v>
+      </c>
+      <c r="P9" t="n">
+        <v>810</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1356046686219929</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.101153684173957</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>39364</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>39881</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>40581</v>
-      </c>
-      <c r="M9" t="n">
-        <v>839</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.4028865261537453</v>
-      </c>
-      <c r="P9" t="n">
-        <v>838</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1777961907160986</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09810389371974938</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>43364</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -4258,40 +4265,38 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>355</v>
+        <v>582</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-55</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.2810219894515295</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.4028865261537453</v>
+        <v>-0.3250537462336849</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>484</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-376</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.6747235555724218</v>
+        <v>0.3908631214425495</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>-0.0321193619836732</v>
+        <v>-0.004234110848904682</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.06234945689994187</v>
+        <v>0.01412727848807149</v>
       </c>
       <c r="AH9" t="n">
-        <v>-260</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -4598,34 +4603,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>43570</v>
+        <v>41124</v>
       </c>
       <c r="M2" t="n">
-        <v>140</v>
+        <v>1215</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="P2" t="n">
-        <v>132</v>
+        <v>1213</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>0.0826944425385638</v>
+        <v>0.2354171526922748</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.05218963375687856</v>
+        <v>0.1563175570682506</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -4635,22 +4640,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.195436869366569</v>
+        <v>-0.5035092528573142</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.202297991486007</v>
+        <v>-0.5040024023286778</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>76</v>
+        <v>860</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -4659,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2429105460160745</v>
+        <v>1.014136226616548</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -4707,34 +4712,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>43559</v>
+        <v>40956</v>
       </c>
       <c r="M3" t="n">
-        <v>133</v>
+        <v>1099</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="P3" t="n">
-        <v>131</v>
+        <v>1098</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.2062376999383152</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.1302468618407874</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -4744,31 +4749,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4652359830536872</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>69</v>
+        <v>744</v>
       </c>
       <c r="AC3" t="n">
-        <v>-7</v>
+        <v>-116</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.8699837092823584</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -4832,34 +4837,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>43458</v>
+        <v>39412</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>43559</v>
+        <v>41306</v>
       </c>
       <c r="M4" t="n">
-        <v>133</v>
+        <v>1338</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>-0.1464423397562968</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="P4" t="n">
-        <v>131</v>
+        <v>1337</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.04836031164019639</v>
+        <v>0.03418961092914297</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0.02975362321475316</v>
+        <v>0.02382249893625346</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -4869,40 +4874,40 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-322</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.1464423397562968</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.1465009124724217</v>
+        <v>-0.07484522873722499</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>69</v>
+        <v>1305</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7</v>
+        <v>445</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.1715670148335209</v>
+        <v>0.08090022454844625</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-2.42861286636753e-17</v>
+        <v>-0.1064243629045339</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0.3903907543164622</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -4957,34 +4962,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>43559</v>
+        <v>40582</v>
       </c>
       <c r="M5" t="n">
-        <v>133</v>
+        <v>840</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="P5" t="n">
-        <v>131</v>
+        <v>839</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>0.04836031164019643</v>
+        <v>0.1784433268325408</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.02975362321475319</v>
+        <v>0.09853741806554034</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -4994,40 +4999,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>69</v>
+        <v>485</v>
       </c>
       <c r="AC5" t="n">
-        <v>-7</v>
+        <v>-375</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.6747235555724218</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0</v>
+        <v>-0.03170944377524706</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0</v>
+        <v>0.06234945689994187</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -5082,76 +5087,80 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+        <v>39881</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>40028</v>
+      </c>
       <c r="M6" t="n">
-        <v>353</v>
+        <v>457</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>-0.1464423397562972</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="P6" t="n">
-        <v>352</v>
+        <v>456</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.07082544091672376</v>
+        <v>0.07583002456742177</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>0.07082544091672376</v>
+        <v>0.03090130387370564</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-0.03485302458783623</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.1464423397562972</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.1465009124724215</v>
+        <v>-0.2597293361904731</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC6" t="inlineStr"/>
+        <v>102</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-758</v>
+      </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.1715670148335213</v>
+        <v>0.3508572592271493</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.04107181770197057</v>
+        <v>-0.09934555796708176</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>1.110223024625157e-16</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>0.2055066468632141</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-642</v>
+      </c>
       <c r="AI6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -5203,34 +5212,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>43585</v>
+        <v>40637</v>
       </c>
       <c r="M7" t="n">
-        <v>150</v>
+        <v>878</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="P7" t="n">
-        <v>148</v>
+        <v>877</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.0472512693456853</v>
+        <v>0.1790468553513548</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.03086031270421815</v>
+        <v>0.1010797139917661</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -5240,40 +5249,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.420671694862634</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>86</v>
+        <v>523</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>-337</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.7261369609118054</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.001106689489464963</v>
+        <v>-0.02916714784902127</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0</v>
+        <v>0.04456428819105318</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>-221</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -5328,76 +5337,80 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>43458</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+        <v>40361</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>40479</v>
+      </c>
       <c r="M8" t="n">
-        <v>353</v>
+        <v>770</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>-0.1464423397562969</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="P8" t="n">
-        <v>352</v>
+        <v>769</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.07082544091672391</v>
+        <v>0.04928794849378988</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0.07082544091672391</v>
+        <v>0.02605978330196763</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-0.03485302458783579</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>64</v>
+        <v>688</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.1464423397562969</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.1465009124724218</v>
+        <v>-0.1432282814604922</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>289</v>
-      </c>
-      <c r="AC8" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-778</v>
+      </c>
       <c r="AD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.1715670148335211</v>
+        <v>0.1671720463703512</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>0.04107181770197072</v>
+        <v>-0.1041870785388198</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>3.33066907387547e-16</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>0.322007701593195</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-662</v>
+      </c>
       <c r="AI8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -5449,34 +5462,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>43364</v>
+        <v>39364</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>43458</v>
+        <v>39881</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>43585</v>
+        <v>40581</v>
       </c>
       <c r="M9" t="n">
-        <v>150</v>
+        <v>839</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="P9" t="n">
-        <v>148</v>
+        <v>838</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.0472512693456853</v>
+        <v>0.1777961907160986</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.03086031270421815</v>
+        <v>0.0981216774403196</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>43880</v>
+        <v>43363</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -5486,40 +5499,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>64</v>
+        <v>355</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.1464423397562973</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.1465009124724216</v>
+        <v>-0.4028865261537453</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>86</v>
+        <v>484</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>-376</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.1715670148335215</v>
+        <v>0.6747235555724218</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.001106689489464963</v>
+        <v>-0.0321251844004678</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0</v>
+        <v>0.06234945689994187</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>-260</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -5826,34 +5839,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43572</v>
+      </c>
+      <c r="M2" t="n">
+        <v>143</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.1989728318606707</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.202297991486007</v>
+      </c>
+      <c r="P2" t="n">
+        <v>138</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.08183226369428304</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.0521184671904906</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>43992</v>
-      </c>
-      <c r="M2" t="n">
-        <v>78</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2902196151348784</v>
-      </c>
-      <c r="P2" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1403286526425156</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.05728893254440424</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -5863,22 +5876,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.1989728318606707</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2902196151348784</v>
+        <v>-0.202297991486007</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -5887,7 +5900,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4088864968986545</v>
+        <v>0.2483971078320051</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -5935,34 +5948,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M3" t="n">
+        <v>134</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P3" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.04818086645128587</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M3" t="n">
-        <v>122</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -5972,31 +5985,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC3" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -6060,34 +6073,34 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M4" t="n">
+        <v>134</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.146153697786501</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.1465009124724217</v>
+      </c>
+      <c r="P4" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.04818086645128586</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M4" t="n">
-        <v>122</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.2902464771828117</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.2902464771828117</v>
-      </c>
-      <c r="P4" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.1177175505348944</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0.05996593388725455</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
@@ -6097,34 +6110,34 @@
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.146153697786501</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>-0.2902464771828117</v>
+        <v>-0.1465009124724217</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC4" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0.4089398190385181</v>
+        <v>0.1711709676643376</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-3.469446951953614e-17</v>
+        <v>-3.469446951953614e-18</v>
       </c>
       <c r="AG4" s="3" t="n">
         <v>2.220446049250313e-16</v>
@@ -6185,34 +6198,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="M5" t="n">
+        <v>134</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P5" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.04818086645128587</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.02971168714991625</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M5" t="n">
-        <v>122</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P5" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -6222,31 +6235,31 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="AC5" t="n">
-        <v>44</v>
+        <v>-9</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF5" s="3" t="n">
         <v>0</v>
@@ -6310,80 +6323,76 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>354</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.1461536977865011</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P6" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.07072561642607446</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.07072561642607446</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K6" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M6" t="n">
-        <v>122</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P6" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1177175505348944</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.05996593388725456</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="b">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>-0.03452664719460175</v>
+      </c>
       <c r="W6" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865011</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>44</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643376</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-2.775557561562891e-17</v>
+        <v>0.04101392927615821</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" s="3" t="inlineStr"/>
       <c r="AK6" s="3" t="inlineStr"/>
@@ -6435,34 +6444,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>43585</v>
+      </c>
+      <c r="M7" t="n">
+        <v>151</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P7" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.04709558104979821</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.03081681682255319</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M7" t="n">
-        <v>122</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P7" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -6472,40 +6481,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="AC7" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0</v>
+        <v>0.001105129672636943</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -6560,80 +6569,76 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>354</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.1461536977865011</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P8" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.07072561642607431</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.07072561642607431</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M8" t="n">
-        <v>122</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>-0.290246477182812</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.290246477182812</v>
-      </c>
-      <c r="P8" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.1177175505348944</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.05996593388725454</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>44564</v>
-      </c>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
-      </c>
-      <c r="V8" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>-0.03452664719460152</v>
+      </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1461536977865011</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>-0.290246477182812</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>99</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>44</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0.4089398190385187</v>
+        <v>0.1711709676643376</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-4.85722573273506e-17</v>
+        <v>0.04101392927615806</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>-1.110223024625157e-16</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
+        <v>1.110223024625157e-16</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" s="3" t="inlineStr"/>
       <c r="AK8" s="3" t="inlineStr"/>
@@ -6685,34 +6690,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43458</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>43585</v>
+      </c>
+      <c r="M9" t="n">
+        <v>151</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.1461536977865012</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.1465009124724216</v>
+      </c>
+      <c r="P9" t="n">
+        <v>147</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.04709558104979821</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.03081681682255319</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>43880</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>43913</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>44055</v>
-      </c>
-      <c r="M9" t="n">
-        <v>122</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2902464771828119</v>
-      </c>
-      <c r="P9" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.1177175505348945</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.05996593388725459</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>44564</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -6722,40 +6727,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1461536977865012</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2902464771828119</v>
+        <v>-0.1465009124724216</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="AC9" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.4089398190385185</v>
+        <v>0.1711709676643378</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0</v>
+        <v>0.001105129672636943</v>
       </c>
       <c r="AG9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -7062,34 +7067,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>43992</v>
+      </c>
+      <c r="M2" t="n">
+        <v>78</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2902196151348784</v>
+      </c>
+      <c r="P2" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1403286526425156</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.05728893254440424</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>44931</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45250</v>
-      </c>
-      <c r="M2" t="n">
-        <v>473</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.3239608533428747</v>
-      </c>
-      <c r="P2" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1873955345996989</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.1456175032694574</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -7099,22 +7104,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>253</v>
+        <v>23</v>
       </c>
       <c r="X2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.3239608533428747</v>
+        <v>-0.2902196151348784</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -7123,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.4792042812088539</v>
+        <v>0.4088864968986545</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -7171,34 +7176,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M3" t="n">
+        <v>122</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P3" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45121</v>
-      </c>
-      <c r="M3" t="n">
-        <v>383</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="P3" t="n">
-        <v>382</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.1328475678049171</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.09291469197671884</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -7208,31 +7213,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="AC3" t="n">
-        <v>-32</v>
+        <v>44</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -7296,73 +7301,77 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M4" t="n">
+        <v>122</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-0.2902464771828117</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>-0.2902464771828117</v>
+      </c>
+      <c r="P4" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.1177175505348944</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.05996593388725455</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>513</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>-0.006696816304247677</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0.0003872733026600608</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" s="3" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X4" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>0</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0</v>
+        <v>-0.2902464771828117</v>
       </c>
       <c r="AA4" t="b">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AC4" t="n">
-        <v>-220</v>
+        <v>44</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>0</v>
+        <v>0.4089398190385181</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.09291469197671884</v>
+        <v>-3.469446951953614e-17</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.2382824194485816</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="AH4" t="n">
-        <v>-188</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -7371,12 +7380,8 @@
       <c r="AK4" s="3" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
-      <c r="AN4" s="3" t="n">
-        <v>0.2383076748178463</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>-0.1920793993641633</v>
-      </c>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7421,34 +7426,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M5" t="n">
+        <v>122</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P5" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M5" t="n">
-        <v>425</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="P5" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.135142485096232</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.09955472383307543</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -7458,40 +7463,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>230</v>
+        <v>99</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.006640031856356587</v>
+        <v>0</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.009858841505368088</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -7500,12 +7505,8 @@
       <c r="AK5" s="3" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
-      <c r="AN5" s="3" t="n">
-        <v>0.2383076748178463</v>
-      </c>
-      <c r="AO5" s="3" t="n">
-        <v>-0.02819104197355771</v>
-      </c>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7550,34 +7551,34 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M6" t="n">
+        <v>122</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P6" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1177175505348944</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.05996593388725456</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>45427</v>
-      </c>
-      <c r="M6" t="n">
-        <v>594</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>-0.2382824194485826</v>
-      </c>
-      <c r="P6" t="n">
-        <v>593</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0.1332546418439375</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.1160128246035556</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
@@ -7587,40 +7588,40 @@
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>-0.2382824194485826</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>399</v>
+        <v>99</v>
       </c>
       <c r="AC6" t="n">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0.3128225283655484</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>0.02309813262683674</v>
+        <v>-2.775557561562891e-17</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>-9.992007221626409e-16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -7675,34 +7676,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M7" t="n">
+        <v>122</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P7" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M7" t="n">
-        <v>425</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.2382824194485816</v>
-      </c>
-      <c r="P7" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.1358689911275819</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.100089915318289</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -7712,40 +7713,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.2382824194485816</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>230</v>
+        <v>99</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.3128225283655466</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.007175223341570156</v>
+        <v>0</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -7800,73 +7801,77 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M8" t="n">
+        <v>122</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>-0.290246477182812</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>-0.290246477182812</v>
+      </c>
+      <c r="P8" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.1177175505348944</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0.05996593388725454</v>
+      </c>
+      <c r="S8" s="2" t="n">
         <v>44564</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>513</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>-0.006696816304248121</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.0003872733026600894</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>45707</v>
-      </c>
       <c r="T8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="V8" s="3" t="inlineStr"/>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X8" t="n">
-        <v>-195</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>0</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>0</v>
+        <v>-0.290246477182812</v>
       </c>
       <c r="AA8" t="b">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="AC8" t="n">
-        <v>-220</v>
+        <v>44</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>0</v>
+        <v>0.4089398190385187</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.09291469197671884</v>
+        <v>-4.85722573273506e-17</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.2382824194485816</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="AH8" t="n">
-        <v>-188</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -7921,34 +7926,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>43880</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>43913</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>44055</v>
+      </c>
+      <c r="M9" t="n">
+        <v>122</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2902464771828119</v>
+      </c>
+      <c r="P9" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.1177175505348945</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05996593388725459</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>44564</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>44846</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45182</v>
-      </c>
-      <c r="M9" t="n">
-        <v>425</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.2284235779432136</v>
-      </c>
-      <c r="P9" t="n">
-        <v>424</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.135142485096232</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.09955472383307543</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>45707</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -7958,40 +7963,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>195</v>
+        <v>23</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.2284235779432136</v>
+        <v>-0.2902464771828119</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>230</v>
+        <v>99</v>
       </c>
       <c r="AC9" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.2960478980608379</v>
+        <v>0.4089398190385185</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.006640031856356587</v>
+        <v>0</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.009858841505368088</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -8298,34 +8303,34 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>44931</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45250</v>
+      </c>
+      <c r="M2" t="n">
+        <v>473</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.3239608533428747</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1873955345996989</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.1456175032694574</v>
+      </c>
+      <c r="S2" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>45835</v>
-      </c>
-      <c r="M2" t="n">
-        <v>89</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>-0.2242012270138071</v>
-      </c>
-      <c r="P2" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0.1032426212645815</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>0.06633642004451827</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
@@ -8335,22 +8340,22 @@
       </c>
       <c r="V2" s="3" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="Y2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>-0.2242012270138071</v>
+        <v>-0.3239608533428747</v>
       </c>
       <c r="AA2" t="b">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>55</v>
+        <v>220</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -8359,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>0.2889940469367012</v>
+        <v>0.4792042812088539</v>
       </c>
       <c r="AF2" s="3" t="inlineStr"/>
       <c r="AG2" s="3" t="inlineStr"/>
@@ -8407,34 +8412,34 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45121</v>
+      </c>
+      <c r="M3" t="n">
+        <v>383</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="P3" t="n">
+        <v>382</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.1328475678049171</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.09291469197671884</v>
+      </c>
+      <c r="S3" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>45863</v>
-      </c>
-      <c r="M3" t="n">
-        <v>108</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>-0.1556116196127491</v>
-      </c>
-      <c r="P3" t="n">
-        <v>107</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0.06372707386676911</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0.04506184607636846</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T3" t="b">
         <v>0</v>
@@ -8444,31 +8449,31 @@
       </c>
       <c r="V3" s="3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>-0.1556116196127491</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="AA3" t="b">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="AC3" t="n">
-        <v>19</v>
+        <v>-32</v>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>0.184289153222813</v>
+        <v>0.3128225283655466</v>
       </c>
       <c r="AF3" s="3" t="n">
         <v>0</v>
@@ -8532,30 +8537,30 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>0</v>
+        <v>-0.006696816304247677</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0</v>
+        <v>0.0003872733026600608</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -8568,7 +8573,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>0</v>
@@ -8583,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
@@ -8592,13 +8597,13 @@
         <v>0</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>-0.04506184607636846</v>
+        <v>-0.09291469197671884</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>0.1556116196127491</v>
+        <v>0.2382824194485816</v>
       </c>
       <c r="AH4" t="n">
-        <v>-74</v>
+        <v>-188</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -8608,10 +8613,10 @@
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" s="3" t="n">
-        <v>0.06587707306593171</v>
+        <v>0.2383076748178463</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.05707000491572423</v>
+        <v>-0.1920793993641633</v>
       </c>
     </row>
     <row r="5">
@@ -8657,34 +8662,34 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="M5" t="n">
+        <v>425</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="P5" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.135142485096232</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.09955472383307543</v>
+      </c>
+      <c r="S5" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M5" t="n">
-        <v>140</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P5" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
@@ -8694,40 +8699,40 @@
       </c>
       <c r="V5" s="3" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA5" t="b">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AC5" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>0.004991043952540582</v>
+        <v>0.006640031856356587</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>0.03053508206683808</v>
+        <v>0.009858841505368088</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -8737,10 +8742,10 @@
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" s="3" t="n">
-        <v>0.06587707306593171</v>
+        <v>0.2383076748178463</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>0.002524191693261901</v>
+        <v>-0.02819104197355771</v>
       </c>
     </row>
     <row r="6">
@@ -8786,73 +8791,77 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>45427</v>
+      </c>
+      <c r="M6" t="n">
+        <v>594</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>-0.2382824194485826</v>
+      </c>
+      <c r="P6" t="n">
+        <v>593</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.1332546418439375</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.1160128246035556</v>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>88</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>46021</v>
-      </c>
       <c r="T6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
       <c r="V6" s="3" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="X6" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>0</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0</v>
+        <v>-0.2382824194485826</v>
       </c>
       <c r="AA6" t="b">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="AC6" t="n">
-        <v>-55</v>
+        <v>179</v>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>0</v>
+        <v>0.3128225283655484</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>-0.04506184607636846</v>
+        <v>0.02309813262683674</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>0.1556116196127491</v>
+        <v>-9.992007221626409e-16</v>
       </c>
       <c r="AH6" t="n">
-        <v>-74</v>
+        <v>211</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -8861,12 +8870,8 @@
       <c r="AK6" s="3" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
-      <c r="AN6" s="3" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>-0.05707000491572423</v>
-      </c>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8911,34 +8916,34 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="M7" t="n">
+        <v>425</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.2382824194485816</v>
+      </c>
+      <c r="P7" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.1358689911275819</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.100089915318289</v>
+      </c>
+      <c r="S7" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M7" t="n">
-        <v>140</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P7" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T7" t="b">
         <v>0</v>
@@ -8948,40 +8953,40 @@
       </c>
       <c r="V7" s="3" t="inlineStr"/>
       <c r="W7" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2382824194485816</v>
       </c>
       <c r="AA7" t="b">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AC7" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.3128225283655466</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>0.004991043952540582</v>
+        <v>0.007175223341570156</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>0.03053508206683808</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -8990,12 +8995,8 @@
       <c r="AK7" s="3" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="inlineStr"/>
-      <c r="AN7" s="3" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AO7" s="3" t="n">
-        <v>0.002524191693261901</v>
-      </c>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9040,30 +9041,30 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>45707</v>
+        <v>44564</v>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>88</v>
+        <v>513</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0</v>
+        <v>-0.006696816304248121</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0</v>
+        <v>0.0003872733026600894</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>46021</v>
+        <v>45707</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -9076,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-34</v>
+        <v>-195</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>0</v>
@@ -9091,7 +9092,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-55</v>
+        <v>-220</v>
       </c>
       <c r="AD8" t="b">
         <v>0</v>
@@ -9100,13 +9101,13 @@
         <v>0</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>-0.04506184607636846</v>
+        <v>-0.09291469197671884</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>0.1556116196127491</v>
+        <v>0.2382824194485816</v>
       </c>
       <c r="AH8" t="n">
-        <v>-74</v>
+        <v>-188</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -9115,12 +9116,8 @@
       <c r="AK8" s="3" t="inlineStr"/>
       <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="inlineStr"/>
-      <c r="AN8" s="3" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>-0.05707000491572423</v>
-      </c>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9165,34 +9162,34 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>44564</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>44846</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="M9" t="n">
+        <v>425</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.2284235779432136</v>
+      </c>
+      <c r="P9" t="n">
+        <v>424</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.135142485096232</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.09955472383307543</v>
+      </c>
+      <c r="S9" s="2" t="n">
         <v>45707</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>45755</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="M9" t="n">
-        <v>140</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="O9" s="3" t="n">
-        <v>-0.125076537545911</v>
-      </c>
-      <c r="P9" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>0.0622368851691482</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>0.05005289002890904</v>
-      </c>
-      <c r="S9" s="2" t="n">
-        <v>46021</v>
       </c>
       <c r="T9" t="b">
         <v>0</v>
@@ -9202,40 +9199,40 @@
       </c>
       <c r="V9" s="3" t="inlineStr"/>
       <c r="W9" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>-0.125076537545911</v>
+        <v>-0.2284235779432136</v>
       </c>
       <c r="AA9" t="b">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="AC9" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>0.142957119009109</v>
+        <v>0.2960478980608379</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>0.004991043952540582</v>
+        <v>0.006640031856356587</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>0.03053508206683808</v>
+        <v>0.009858841505368088</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -9244,12 +9241,8 @@
       <c r="AK9" s="3" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="inlineStr"/>
-      <c r="AN9" s="3" t="n">
-        <v>0.06587707306593171</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>0.002524191693261901</v>
-      </c>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9262,7 +9255,1255 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:AO9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+    <col width="17" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="19" customWidth="1" min="29" max="29"/>
+    <col width="23" customWidth="1" min="30" max="30"/>
+    <col width="20" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="14" customWidth="1" min="40" max="40"/>
+    <col width="17" customWidth="1" min="41" max="41"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>base_run</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fallback_run</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>crisis_target</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>peak_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>trough_date</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>recovery_date</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>full_days</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>full_anchored_dd</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>full_hwm_dd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>full_days_underwater</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>full_ulcer_common</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>full_common_end</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>full_no_drawdown</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_not_recovered</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_gap_at_cutoff</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_days_vs_defined</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_depth</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_max_dd</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_trough_at_boundary</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_days_vs_bench</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_vs_bench_censored</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_return_to_even</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_base_ulcer</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_base_depth</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_days</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_base_censored</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>full_d_fb_ulcer</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>ptt_d_fb_depth</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_days</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_d_fb_censored</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>missed_rally</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pre_peak_d_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mcap_t_10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>45835</v>
+      </c>
+      <c r="M2" t="n">
+        <v>89</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="P2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.1032426212645815</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.06633642004451827</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>-0.2242012270138071</v>
+      </c>
+      <c r="AA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0.2889940469367012</v>
+      </c>
+      <c r="AF2" s="3" t="inlineStr"/>
+      <c r="AG2" s="3" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" s="3" t="inlineStr"/>
+      <c r="AK2" s="3" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>45863</v>
+      </c>
+      <c r="M3" t="n">
+        <v>108</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="P3" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.06372707386676911</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.04506184607636846</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>34</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>-0.1556116196127491</v>
+      </c>
+      <c r="AA3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>74</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0.184289153222813</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_cash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>89</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="3" t="n">
+        <v>-0.04506184607636846</v>
+      </c>
+      <c r="AG4" s="3" t="n">
+        <v>0.1556116196127491</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO4" s="3" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_changepoint_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>changepoint</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="M5" t="n">
+        <v>140</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="P5" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.0622368851691482</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.05005289002890904</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>34</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="AA5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>106</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="3" t="n">
+        <v>0.142957119009109</v>
+      </c>
+      <c r="AF5" s="3" t="n">
+        <v>0.004991043952540582</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>0.03053508206683808</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO5" s="3" t="n">
+        <v>0.002524191693261901</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_cash</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>89</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="3" t="n">
+        <v>-0.04506184607636846</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>0.1556116196127491</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO6" s="3" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_hmm_gspc_min_var</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>hmm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>gspc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="M7" t="n">
+        <v>140</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="P7" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.0622368851691482</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.05005289002890904</v>
+      </c>
+      <c r="S7" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>34</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>106</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0.142957119009109</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0.004991043952540582</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0.03053508206683808</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO7" s="3" t="n">
+        <v>0.002524191693261901</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_cash</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>89</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="inlineStr"/>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-34</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-55</v>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>-0.04506184607636846</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0.1556116196127491</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-74</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO8" s="3" t="n">
+        <v>-0.05707000491572423</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>hrp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward_wasserstein_gspc_vix_min_var</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>regime</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hrp_t_10_lw_ward</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>min_var</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>45707</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>45755</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="M9" t="n">
+        <v>140</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="P9" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>0.0622368851691482</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.05005289002890904</v>
+      </c>
+      <c r="S9" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" t="n">
+        <v>34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-0.125076537545911</v>
+      </c>
+      <c r="AA9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>106</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>51</v>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>0.142957119009109</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>0.004991043952540582</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0.03053508206683808</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" s="3" t="n">
+        <v>0.06587707306593171</v>
+      </c>
+      <c r="AO9" s="3" t="n">
+        <v>0.002524191693261901</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9368,12 +10609,8 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>563</v>
-      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
       <c r="G2" t="n">
         <v>0</v>
       </c>
@@ -9382,10 +10619,10 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>0.5562326869806095</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -9416,10 +10653,10 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>963</v>
+        <v>563</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -9429,7 +10666,7 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" s="3" t="n">
-        <v>0.9149709302325582</v>
+        <v>0.5568496949528563</v>
       </c>
       <c r="K3" t="n">
         <v>2</v>
@@ -9462,8 +10699,12 @@
           <t>C3</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>963</v>
+      </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
@@ -9472,10 +10713,10 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.9149709302325582</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -9548,24 +10789,20 @@
           <t>C5</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>-251</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>307</v>
-      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -9596,21 +10833,23 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr"/>
+        <v>-251</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>307</v>
+      </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>251</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -9627,30 +10866,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hmm</t>
+          <t>changepoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gspc</t>
+          <t>vix</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr"/>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-30</v>
+      </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -9680,15 +10921,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-43</v>
-      </c>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -9697,10 +10934,10 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" s="3" t="n">
-        <v>0.3655523255813953</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -9727,7 +10964,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
@@ -9736,16 +10973,14 @@
         <v>0</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" s="3" t="n">
-        <v>0.5241379310344828</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -9772,11 +11007,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr"/>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-43</v>
+      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
@@ -9785,10 +11024,10 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>0.3655523255813953</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -9815,7 +11054,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
@@ -9827,13 +11066,13 @@
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.4873294346978557</v>
+        <v>0.5205479452054794</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -9860,22 +11099,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -9895,37 +11132,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-193</v>
-      </c>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57</v>
+      </c>
       <c r="J14" s="3" t="n">
-        <v>0.2770083102493075</v>
+        <v>0.4873294346978557</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -9942,37 +11177,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wasserstein</t>
+          <t>hmm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>gspc_vix</t>
+          <t>gspc</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>59</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>209</v>
-      </c>
+        <v>-30</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H15" t="b">
         <v>0</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" s="3" t="n">
-        <v>0.3670058139534884</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -9999,25 +11232,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-134</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>339</v>
+      </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.5241379310344828</v>
-      </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -10044,11 +11279,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-193</v>
+      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
@@ -10057,10 +11296,10 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>0.2773155851358846</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10087,14 +11326,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -10104,7 +11343,7 @@
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" s="3" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.3670058139534884</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -10134,30 +11373,165 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C6</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-30</v>
-      </c>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
       <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
       <c r="J19" s="3" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
       </c>
       <c r="M19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="3" t="n">
+        <v>0.9766081871345029</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>yearly</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>wasserstein</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gspc_vix</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="b">
         <v>1</v>
       </c>
     </row>
